--- a/UBER.xlsx
+++ b/UBER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F653AE1-7B2E-416A-86D7-344C5A23576A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AFB5B8F-9B03-482E-BF3C-02F6E7101A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" xr2:uid="{A6A9719B-65E6-4B85-BB9B-7231670B31D1}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{A6A9719B-65E6-4B85-BB9B-7231670B31D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -257,13 +257,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -327,26 +333,29 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -703,7 +712,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="2">
-        <v>90.18</v>
+        <v>74.88</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -711,10 +720,10 @@
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>2085.4186759999998</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>67</v>
+        <v>2077.8303810000002</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -726,7 +735,7 @@
       </c>
       <c r="H4" s="5">
         <f>+H2*H3</f>
-        <v>188063.05620167998</v>
+        <v>155587.93892928</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -737,11 +746,11 @@
         <v>4</v>
       </c>
       <c r="H5" s="5">
-        <f>5893+1084</f>
-        <v>6977</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>67</v>
+        <f>8432+654</f>
+        <v>9086</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -749,10 +758,10 @@
         <v>5</v>
       </c>
       <c r="H6" s="5">
-        <v>8347</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>67</v>
+        <v>10615</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -764,7 +773,7 @@
       </c>
       <c r="H7" s="5">
         <f>+H4-H5+H6</f>
-        <v>189433.05620167998</v>
+        <v>157116.93892928</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -907,7 +916,9 @@
       <c r="L3" s="5">
         <v>180</v>
       </c>
-      <c r="M3" s="5"/>
+      <c r="M3" s="5">
+        <v>189</v>
+      </c>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
@@ -1001,7 +1012,9 @@
       <c r="L4" s="5">
         <v>3268</v>
       </c>
-      <c r="M4" s="5"/>
+      <c r="M4" s="5">
+        <v>3512</v>
+      </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
@@ -1095,7 +1108,9 @@
       <c r="L5" s="5">
         <v>46756</v>
       </c>
-      <c r="M5" s="5"/>
+      <c r="M5" s="5">
+        <v>49740</v>
+      </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
@@ -1164,7 +1179,7 @@
         <v>0.28091569026999491</v>
       </c>
       <c r="D6" s="6">
-        <f t="shared" ref="D6:L6" si="0">+D11/D5</f>
+        <f t="shared" ref="D6:M6" si="0">+D11/D5</f>
         <v>0.27469420552959734</v>
       </c>
       <c r="E6" s="6">
@@ -1199,7 +1214,10 @@
         <f t="shared" si="0"/>
         <v>0.27057489947814184</v>
       </c>
-      <c r="M6" s="6"/>
+      <c r="M6" s="6">
+        <f t="shared" si="0"/>
+        <v>0.27074788902291919</v>
+      </c>
       <c r="N6" s="6"/>
       <c r="O6" s="5"/>
       <c r="P6" s="6" t="e">
@@ -1368,7 +1386,9 @@
       <c r="L8" s="5">
         <v>7288</v>
       </c>
-      <c r="M8" s="5"/>
+      <c r="M8" s="5">
+        <v>7682</v>
+      </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
@@ -1464,7 +1484,9 @@
       <c r="L9" s="5">
         <v>4102</v>
       </c>
-      <c r="M9" s="5"/>
+      <c r="M9" s="5">
+        <v>4477</v>
+      </c>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
@@ -1560,7 +1582,9 @@
       <c r="L10" s="5">
         <v>1261</v>
       </c>
-      <c r="M10" s="5"/>
+      <c r="M10" s="5">
+        <v>1308</v>
+      </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
@@ -1657,7 +1681,9 @@
       <c r="L11" s="8">
         <v>12651</v>
       </c>
-      <c r="M11" s="8"/>
+      <c r="M11" s="8">
+        <v>13467</v>
+      </c>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -1755,7 +1781,9 @@
       <c r="L12" s="5">
         <v>7611</v>
       </c>
-      <c r="M12" s="5"/>
+      <c r="M12" s="5">
+        <v>8109</v>
+      </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
@@ -1846,7 +1874,7 @@
         <v>4212</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" ref="I13:L13" si="10">+I11-I12</f>
+        <f t="shared" ref="I13:M13" si="10">+I11-I12</f>
         <v>4427</v>
       </c>
       <c r="J13" s="5">
@@ -1861,7 +1889,10 @@
         <f t="shared" si="10"/>
         <v>5040</v>
       </c>
-      <c r="M13" s="5"/>
+      <c r="M13" s="5">
+        <f>+M11-M12</f>
+        <v>5358</v>
+      </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
       <c r="P13" s="5">
@@ -1967,7 +1998,9 @@
       <c r="L14" s="5">
         <v>696</v>
       </c>
-      <c r="M14" s="5"/>
+      <c r="M14" s="5">
+        <v>735</v>
+      </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
@@ -2065,7 +2098,9 @@
       <c r="L15" s="5">
         <v>1210</v>
       </c>
-      <c r="M15" s="5"/>
+      <c r="M15" s="5">
+        <v>1277</v>
+      </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
@@ -2163,7 +2198,9 @@
       <c r="L16" s="5">
         <v>840</v>
       </c>
-      <c r="M16" s="5"/>
+      <c r="M16" s="5">
+        <v>862</v>
+      </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
@@ -2261,7 +2298,9 @@
       <c r="L17" s="5">
         <v>669</v>
       </c>
-      <c r="M17" s="5"/>
+      <c r="M17" s="5">
+        <v>1183</v>
+      </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
@@ -2359,7 +2398,9 @@
       <c r="L18" s="5">
         <v>175</v>
       </c>
-      <c r="M18" s="5"/>
+      <c r="M18" s="5">
+        <v>188</v>
+      </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
@@ -2465,7 +2506,10 @@
         <f t="shared" si="13"/>
         <v>1450</v>
       </c>
-      <c r="M19" s="5"/>
+      <c r="M19" s="5">
+        <f t="shared" si="13"/>
+        <v>1113</v>
+      </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
       <c r="P19" s="5">
@@ -2569,7 +2613,9 @@
       <c r="L20" s="5">
         <v>108</v>
       </c>
-      <c r="M20" s="5"/>
+      <c r="M20" s="5">
+        <v>112</v>
+      </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
@@ -2665,7 +2711,9 @@
       <c r="L21" s="5">
         <v>162</v>
       </c>
-      <c r="M21" s="5"/>
+      <c r="M21" s="5">
+        <v>1619</v>
+      </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
@@ -2771,7 +2819,10 @@
         <f t="shared" si="15"/>
         <v>1504</v>
       </c>
-      <c r="M22" s="5"/>
+      <c r="M22" s="5">
+        <f t="shared" si="15"/>
+        <v>2620</v>
+      </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5">
@@ -2875,7 +2926,9 @@
       <c r="L23" s="5">
         <v>142</v>
       </c>
-      <c r="M23" s="5"/>
+      <c r="M23" s="5">
+        <v>-4046</v>
+      </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
@@ -2971,7 +3024,9 @@
       <c r="L24" s="5">
         <v>-12</v>
       </c>
-      <c r="M24" s="5"/>
+      <c r="M24" s="5">
+        <v>-14</v>
+      </c>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
@@ -3077,7 +3132,10 @@
         <f t="shared" si="17"/>
         <v>1350</v>
       </c>
-      <c r="M25" s="5"/>
+      <c r="M25" s="5">
+        <f t="shared" si="17"/>
+        <v>6652</v>
+      </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
       <c r="P25" s="5">
@@ -3181,7 +3239,9 @@
       <c r="L26" s="5">
         <v>-5</v>
       </c>
-      <c r="M26" s="5"/>
+      <c r="M26" s="5">
+        <v>26</v>
+      </c>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
       <c r="P26" s="5"/>
@@ -3287,7 +3347,10 @@
         <f t="shared" si="19"/>
         <v>1355</v>
       </c>
-      <c r="M27" s="5"/>
+      <c r="M27" s="5">
+        <f t="shared" si="19"/>
+        <v>6626</v>
+      </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
       <c r="P27" s="5">
@@ -3453,7 +3516,7 @@
         <v>1.2304559253161786</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" ref="J29:L29" si="21">+J27/J30</f>
+        <f t="shared" ref="J29:M29" si="21">+J27/J30</f>
         <v>3.3008657491972224</v>
       </c>
       <c r="K29" s="9">
@@ -3464,7 +3527,10 @@
         <f t="shared" si="21"/>
         <v>0.6479824552174781</v>
       </c>
-      <c r="M29" s="9"/>
+      <c r="M29" s="9">
+        <f t="shared" si="21"/>
+        <v>3.1791879780057388</v>
+      </c>
       <c r="N29" s="9"/>
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
@@ -3567,7 +3633,9 @@
       <c r="L30" s="5">
         <v>2091.1060000000002</v>
       </c>
-      <c r="M30" s="5"/>
+      <c r="M30" s="5">
+        <v>2084.1799999999998</v>
+      </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
@@ -3701,7 +3769,7 @@
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="6">
-        <f t="shared" ref="G32:L34" si="23">+G3/C3-1</f>
+        <f t="shared" ref="G32:M34" si="23">+G3/C3-1</f>
         <v>0.14615384615384608</v>
       </c>
       <c r="H32" s="6">
@@ -3724,7 +3792,10 @@
         <f t="shared" si="23"/>
         <v>0.15384615384615374</v>
       </c>
-      <c r="M32" s="6"/>
+      <c r="M32" s="6">
+        <f t="shared" si="23"/>
+        <v>0.17391304347826098</v>
+      </c>
       <c r="N32" s="6"/>
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
@@ -3823,7 +3894,10 @@
         <f t="shared" si="23"/>
         <v>0.18191681735985532</v>
       </c>
-      <c r="M33" s="6"/>
+      <c r="M33" s="6">
+        <f t="shared" si="23"/>
+        <v>0.22454672245467222</v>
+      </c>
       <c r="N33" s="6"/>
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
@@ -3922,7 +3996,10 @@
         <f t="shared" si="23"/>
         <v>0.17030436523828585</v>
       </c>
-      <c r="M34" s="6"/>
+      <c r="M34" s="6">
+        <f t="shared" si="23"/>
+        <v>0.2139701754814145</v>
+      </c>
       <c r="N34" s="6"/>
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
@@ -4006,7 +4083,7 @@
         <v>0.25337147527584802</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" ref="I35:L38" si="28">I8/E8-1</f>
+        <f t="shared" ref="I35:M38" si="28">I8/E8-1</f>
         <v>0.26385328337605984</v>
       </c>
       <c r="J35" s="6">
@@ -4021,7 +4098,10 @@
         <f t="shared" si="28"/>
         <v>0.18813172481252027</v>
       </c>
-      <c r="M35" s="6"/>
+      <c r="M35" s="6">
+        <f t="shared" si="28"/>
+        <v>0.19862693087845207</v>
+      </c>
       <c r="N35" s="6"/>
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
@@ -4120,7 +4200,10 @@
         <f t="shared" si="28"/>
         <v>0.24567263893106595</v>
       </c>
-      <c r="M36" s="6"/>
+      <c r="M36" s="6">
+        <f t="shared" si="28"/>
+        <v>0.29020172910662834</v>
+      </c>
       <c r="N36" s="6"/>
       <c r="O36" s="5"/>
       <c r="P36" s="6"/>
@@ -4219,7 +4302,10 @@
         <f t="shared" si="28"/>
         <v>-9.4265514532599903E-3</v>
       </c>
-      <c r="M37" s="6"/>
+      <c r="M37" s="6">
+        <f t="shared" si="28"/>
+        <v>-7.6394194041251584E-4</v>
+      </c>
       <c r="N37" s="6"/>
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
@@ -4318,7 +4404,10 @@
         <f t="shared" si="28"/>
         <v>0.18233644859813092</v>
       </c>
-      <c r="M38" s="10"/>
+      <c r="M38" s="10">
+        <f t="shared" si="28"/>
+        <v>0.20370039327851264</v>
+      </c>
       <c r="N38" s="10"/>
       <c r="O38" s="5"/>
       <c r="P38" s="5"/>
@@ -4426,31 +4515,34 @@
         <f t="shared" si="38"/>
         <v>0.3983874792506521</v>
       </c>
-      <c r="M39" s="6"/>
+      <c r="M39" s="6">
+        <f t="shared" ref="M39" si="39">+M13/M11</f>
+        <v>0.39786143907329025</v>
+      </c>
       <c r="N39" s="6"/>
       <c r="O39" s="5"/>
       <c r="P39" s="6" t="e">
-        <f t="shared" ref="P39:U39" si="39">+P13/P11</f>
+        <f t="shared" ref="P39:U39" si="40">+P13/P11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q39" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.5373013735523835</v>
       </c>
       <c r="R39" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.46427957605270698</v>
       </c>
       <c r="S39" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.38328575461931802</v>
       </c>
       <c r="T39" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.39762881896944824</v>
       </c>
       <c r="U39" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.39399245077083994</v>
       </c>
       <c r="V39" s="5"/>
@@ -4501,23 +4593,23 @@
         <v>45</v>
       </c>
       <c r="C40" s="6">
-        <f t="shared" ref="C40:G40" si="40">+C19/C11</f>
+        <f t="shared" ref="C40:G40" si="41">+C19/C11</f>
         <v>-2.9695115040235746E-2</v>
       </c>
       <c r="D40" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>3.5319609967497292E-2</v>
       </c>
       <c r="E40" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>4.240206629358588E-2</v>
       </c>
       <c r="F40" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>6.5619967793880837E-2</v>
       </c>
       <c r="G40" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1.6977593524824794E-2</v>
       </c>
       <c r="H40" s="6">
@@ -4525,46 +4617,49 @@
         <v>7.3925233644859811E-2</v>
       </c>
       <c r="I40" s="6">
-        <f t="shared" ref="I40:J40" si="41">+I19/I11</f>
+        <f t="shared" ref="I40:J40" si="42">+I19/I11</f>
         <v>9.4833750446907394E-2</v>
       </c>
       <c r="J40" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.4804749561000088E-2</v>
       </c>
       <c r="K40" s="6">
-        <f t="shared" ref="K40:L40" si="42">+K19/K11</f>
+        <f t="shared" ref="K40:L40" si="43">+K19/K11</f>
         <v>0.10647706581115061</v>
       </c>
       <c r="L40" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.11461544541933444</v>
       </c>
-      <c r="M40" s="6"/>
+      <c r="M40" s="6">
+        <f t="shared" ref="M40" si="44">+M19/M11</f>
+        <v>8.2646469146803292E-2</v>
+      </c>
       <c r="N40" s="6"/>
       <c r="O40" s="5"/>
       <c r="P40" s="6" t="e">
-        <f t="shared" ref="P40:U40" si="43">+P19/P11</f>
+        <f t="shared" ref="P40:U40" si="45">+P19/P11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q40" s="6">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>-0.43657419876110959</v>
       </c>
       <c r="R40" s="6">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>-0.2196505299341163</v>
       </c>
       <c r="S40" s="6">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>-5.7470903786429085E-2</v>
       </c>
       <c r="T40" s="6">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>2.9773879456023174E-2</v>
       </c>
       <c r="U40" s="6">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>6.3645459093182949E-2</v>
       </c>
       <c r="V40" s="5"/>
@@ -4615,23 +4710,23 @@
         <v>46</v>
       </c>
       <c r="C41" s="6">
-        <f t="shared" ref="C41:G41" si="44">+C23/C22</f>
+        <f t="shared" ref="C41:G41" si="46">+C23/C22</f>
         <v>0</v>
       </c>
       <c r="D41" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="E41" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>-0.22727272727272727</v>
       </c>
       <c r="F41" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>9.6311475409836061E-2</v>
       </c>
       <c r="G41" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>-4.6031746031746035E-2</v>
       </c>
       <c r="H41" s="6">
@@ -4639,46 +4734,49 @@
         <v>5.3171641791044777E-2</v>
       </c>
       <c r="I41" s="6">
-        <f t="shared" ref="I41:J41" si="45">+I23/I22</f>
+        <f t="shared" ref="I41:J41" si="47">+I23/I22</f>
         <v>5.7060310581437339E-2</v>
       </c>
       <c r="J41" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>-6.566739606126915</v>
       </c>
       <c r="K41" s="6">
-        <f t="shared" ref="K41:L41" si="46">+K23/K22</f>
+        <f t="shared" ref="K41:L41" si="48">+K23/K22</f>
         <v>-0.29025270758122745</v>
       </c>
       <c r="L41" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>9.4414893617021281E-2</v>
       </c>
-      <c r="M41" s="6"/>
+      <c r="M41" s="6">
+        <f t="shared" ref="M41" si="49">+M23/M22</f>
+        <v>-1.5442748091603054</v>
+      </c>
       <c r="N41" s="6"/>
       <c r="O41" s="5"/>
       <c r="P41" s="6" t="e">
-        <f t="shared" ref="P41:U41" si="47">+P23/P22</f>
+        <f t="shared" ref="P41:U41" si="50">+P23/P22</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q41" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>2.7641808234955371E-2</v>
       </c>
       <c r="R41" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0.48</v>
       </c>
       <c r="S41" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>1.9202206662423085E-2</v>
       </c>
       <c r="T41" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>9.1770788453252913E-2</v>
       </c>
       <c r="U41" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>-1.3958787878787879</v>
       </c>
       <c r="V41" s="5"/>

--- a/UBER.xlsx
+++ b/UBER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AFB5B8F-9B03-482E-BF3C-02F6E7101A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE221AE-D9CB-4513-BE2E-AC15A111A4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{A6A9719B-65E6-4B85-BB9B-7231670B31D1}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{A6A9719B-65E6-4B85-BB9B-7231670B31D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="71">
   <si>
     <t>numbers in mio USD</t>
   </si>
@@ -248,6 +248,9 @@
   <si>
     <t>Q425</t>
   </si>
+  <si>
+    <t>FY25</t>
+  </si>
 </sst>
 </file>
 
@@ -336,7 +339,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -356,6 +359,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -712,7 +716,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="2">
-        <v>74.88</v>
+        <v>75.69</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -720,10 +724,10 @@
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>2077.8303810000002</v>
+        <v>2058.1159830000001</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -735,7 +739,7 @@
       </c>
       <c r="H4" s="5">
         <f>+H2*H3</f>
-        <v>155587.93892928</v>
+        <v>155778.79875327001</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -746,11 +750,11 @@
         <v>4</v>
       </c>
       <c r="H5" s="5">
-        <f>8432+654</f>
-        <v>9086</v>
+        <f>7105+528</f>
+        <v>7633</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -758,10 +762,10 @@
         <v>5</v>
       </c>
       <c r="H6" s="5">
-        <v>10615</v>
+        <v>10521</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -773,7 +777,7 @@
       </c>
       <c r="H7" s="5">
         <f>+H4-H5+H6</f>
-        <v>157116.93892928</v>
+        <v>158666.79875327001</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -881,6 +885,9 @@
       <c r="U2" s="4" t="s">
         <v>60</v>
       </c>
+      <c r="V2" s="12" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="3" spans="1:63" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -919,7 +926,10 @@
       <c r="M3" s="5">
         <v>189</v>
       </c>
-      <c r="N3" s="5"/>
+      <c r="N3" s="5">
+        <f>+V3</f>
+        <v>202</v>
+      </c>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
@@ -935,7 +945,9 @@
       <c r="U3" s="5">
         <v>171</v>
       </c>
-      <c r="V3" s="5"/>
+      <c r="V3" s="5">
+        <v>202</v>
+      </c>
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
       <c r="Y3" s="5"/>
@@ -1015,7 +1027,10 @@
       <c r="M4" s="5">
         <v>3512</v>
       </c>
-      <c r="N4" s="5"/>
+      <c r="N4" s="5">
+        <f>+V4-SUM(K4:M4)</f>
+        <v>4215</v>
+      </c>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
@@ -1031,7 +1046,9 @@
       <c r="U4" s="5">
         <v>11273</v>
       </c>
-      <c r="V4" s="5"/>
+      <c r="V4" s="5">
+        <v>13567</v>
+      </c>
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
       <c r="Y4" s="5"/>
@@ -1111,7 +1128,10 @@
       <c r="M5" s="5">
         <v>49740</v>
       </c>
-      <c r="N5" s="5"/>
+      <c r="N5" s="5">
+        <f>+V5-SUM(K5:M5)</f>
+        <v>59307</v>
+      </c>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
@@ -1127,7 +1147,9 @@
       <c r="U5" s="5">
         <v>162773</v>
       </c>
-      <c r="V5" s="5"/>
+      <c r="V5" s="5">
+        <v>193454</v>
+      </c>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
       <c r="Y5" s="5"/>
@@ -1179,7 +1201,7 @@
         <v>0.28091569026999491</v>
       </c>
       <c r="D6" s="6">
-        <f t="shared" ref="D6:M6" si="0">+D11/D5</f>
+        <f t="shared" ref="D6:N6" si="0">+D11/D5</f>
         <v>0.27469420552959734</v>
       </c>
       <c r="E6" s="6">
@@ -1218,7 +1240,10 @@
         <f t="shared" si="0"/>
         <v>0.27074788902291919</v>
       </c>
-      <c r="N6" s="6"/>
+      <c r="N6" s="6">
+        <f t="shared" si="0"/>
+        <v>0.24223110256799366</v>
+      </c>
       <c r="O6" s="5"/>
       <c r="P6" s="6" t="e">
         <f t="shared" ref="P6" si="1">+P11/P5</f>
@@ -1241,10 +1266,13 @@
         <v>0.27041671200087042</v>
       </c>
       <c r="U6" s="6">
-        <f t="shared" ref="U6" si="6">+U11/U5</f>
+        <f t="shared" ref="U6:V6" si="6">+U11/U5</f>
         <v>0.27017994384818123</v>
       </c>
-      <c r="V6" s="5"/>
+      <c r="V6" s="6">
+        <f t="shared" si="6"/>
+        <v>0.26888562655721776</v>
+      </c>
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
       <c r="Y6" s="5"/>
@@ -1389,7 +1417,10 @@
       <c r="M8" s="5">
         <v>7682</v>
       </c>
-      <c r="N8" s="5"/>
+      <c r="N8" s="5">
+        <f>+V8-SUM(K8:M8)</f>
+        <v>8204</v>
+      </c>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
@@ -1405,7 +1436,9 @@
       <c r="U8" s="5">
         <v>25087</v>
       </c>
-      <c r="V8" s="5"/>
+      <c r="V8" s="5">
+        <v>29670</v>
+      </c>
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="5"/>
@@ -1487,7 +1520,10 @@
       <c r="M9" s="5">
         <v>4477</v>
       </c>
-      <c r="N9" s="5"/>
+      <c r="N9" s="5">
+        <f>+V9-SUM(K9:M9)</f>
+        <v>4892</v>
+      </c>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
@@ -1503,7 +1539,9 @@
       <c r="U9" s="5">
         <v>13750</v>
       </c>
-      <c r="V9" s="5"/>
+      <c r="V9" s="5">
+        <v>17248</v>
+      </c>
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
       <c r="Y9" s="5"/>
@@ -1585,7 +1623,10 @@
       <c r="M10" s="5">
         <v>1308</v>
       </c>
-      <c r="N10" s="5"/>
+      <c r="N10" s="5">
+        <f>+V10-SUM(K10:M10)</f>
+        <v>1270</v>
+      </c>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
@@ -1602,7 +1643,9 @@
       <c r="U10" s="5">
         <v>5141</v>
       </c>
-      <c r="V10" s="5"/>
+      <c r="V10" s="5">
+        <v>5099</v>
+      </c>
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
       <c r="Y10" s="5"/>
@@ -1684,7 +1727,10 @@
       <c r="M11" s="8">
         <v>13467</v>
       </c>
-      <c r="N11" s="8"/>
+      <c r="N11" s="8">
+        <f>+V11-SUM(K11:M11)</f>
+        <v>14366</v>
+      </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="8">
@@ -1702,7 +1748,9 @@
       <c r="U11" s="8">
         <v>43978</v>
       </c>
-      <c r="V11" s="8"/>
+      <c r="V11" s="8">
+        <v>52017</v>
+      </c>
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
       <c r="Y11" s="8"/>
@@ -1784,7 +1832,10 @@
       <c r="M12" s="5">
         <v>8109</v>
       </c>
-      <c r="N12" s="5"/>
+      <c r="N12" s="5">
+        <f>+V12-SUM(K12:M12)</f>
+        <v>8681</v>
+      </c>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="5">
@@ -1802,7 +1853,9 @@
       <c r="U12" s="5">
         <v>26651</v>
       </c>
-      <c r="V12" s="5"/>
+      <c r="V12" s="5">
+        <v>31338</v>
+      </c>
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="5"/>
@@ -1874,7 +1927,7 @@
         <v>4212</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" ref="I13:M13" si="10">+I11-I12</f>
+        <f t="shared" ref="I13:L13" si="10">+I11-I12</f>
         <v>4427</v>
       </c>
       <c r="J13" s="5">
@@ -1893,7 +1946,10 @@
         <f>+M11-M12</f>
         <v>5358</v>
       </c>
-      <c r="N13" s="5"/>
+      <c r="N13" s="5">
+        <f>+N11-N12</f>
+        <v>5685</v>
+      </c>
       <c r="O13" s="5"/>
       <c r="P13" s="5">
         <f t="shared" ref="P13:S13" si="11">+P11-P12</f>
@@ -1919,7 +1975,10 @@
         <f>+U11-U12</f>
         <v>17327</v>
       </c>
-      <c r="V13" s="5"/>
+      <c r="V13" s="5">
+        <f>+V11-V12</f>
+        <v>20679</v>
+      </c>
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="5"/>
@@ -2001,7 +2060,10 @@
       <c r="M14" s="5">
         <v>735</v>
       </c>
-      <c r="N14" s="5"/>
+      <c r="N14" s="5">
+        <f>+V14-SUM(K14:M14)</f>
+        <v>755</v>
+      </c>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
       <c r="Q14" s="5">
@@ -2019,7 +2081,9 @@
       <c r="U14" s="5">
         <v>2732</v>
       </c>
-      <c r="V14" s="5"/>
+      <c r="V14" s="5">
+        <v>2854</v>
+      </c>
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="5"/>
@@ -2101,7 +2165,10 @@
       <c r="M15" s="5">
         <v>1277</v>
       </c>
-      <c r="N15" s="5"/>
+      <c r="N15" s="5">
+        <f>+V15-SUM(K15:M15)</f>
+        <v>1354</v>
+      </c>
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
       <c r="Q15" s="5">
@@ -2119,7 +2186,9 @@
       <c r="U15" s="5">
         <v>4337</v>
       </c>
-      <c r="V15" s="5"/>
+      <c r="V15" s="5">
+        <v>4898</v>
+      </c>
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
       <c r="Y15" s="5"/>
@@ -2201,7 +2270,10 @@
       <c r="M16" s="5">
         <v>862</v>
       </c>
-      <c r="N16" s="5"/>
+      <c r="N16" s="5">
+        <f>+V16-SUM(K16:M16)</f>
+        <v>885</v>
+      </c>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="5">
@@ -2219,7 +2291,9 @@
       <c r="U16" s="5">
         <v>3109</v>
       </c>
-      <c r="V16" s="5"/>
+      <c r="V16" s="5">
+        <v>3402</v>
+      </c>
       <c r="W16" s="5"/>
       <c r="X16" s="5"/>
       <c r="Y16" s="5"/>
@@ -2301,7 +2375,10 @@
       <c r="M17" s="5">
         <v>1183</v>
       </c>
-      <c r="N17" s="5"/>
+      <c r="N17" s="5">
+        <f>+V17-SUM(K17:M17)</f>
+        <v>732</v>
+      </c>
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
       <c r="Q17" s="5">
@@ -2319,7 +2396,9 @@
       <c r="U17" s="5">
         <v>3639</v>
       </c>
-      <c r="V17" s="5"/>
+      <c r="V17" s="5">
+        <v>3241</v>
+      </c>
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
       <c r="Y17" s="5"/>
@@ -2401,7 +2480,10 @@
       <c r="M18" s="5">
         <v>188</v>
       </c>
-      <c r="N18" s="5"/>
+      <c r="N18" s="5">
+        <f>+V18-SUM(K18:M18)</f>
+        <v>185</v>
+      </c>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5">
@@ -2419,7 +2501,9 @@
       <c r="U18" s="5">
         <v>711</v>
       </c>
-      <c r="V18" s="5"/>
+      <c r="V18" s="5">
+        <v>719</v>
+      </c>
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
       <c r="Y18" s="5"/>
@@ -2491,7 +2575,7 @@
         <v>791</v>
       </c>
       <c r="I19" s="5">
-        <f t="shared" ref="I19:U19" si="13">+I13-SUM(I14:I18)</f>
+        <f t="shared" ref="I19:V19" si="13">+I13-SUM(I14:I18)</f>
         <v>1061</v>
       </c>
       <c r="J19" s="5">
@@ -2510,7 +2594,10 @@
         <f t="shared" si="13"/>
         <v>1113</v>
       </c>
-      <c r="N19" s="5"/>
+      <c r="N19" s="5">
+        <f t="shared" si="13"/>
+        <v>1774</v>
+      </c>
       <c r="O19" s="5"/>
       <c r="P19" s="5">
         <f t="shared" si="13"/>
@@ -2536,7 +2623,10 @@
         <f t="shared" si="13"/>
         <v>2799</v>
       </c>
-      <c r="V19" s="5"/>
+      <c r="V19" s="5">
+        <f t="shared" si="13"/>
+        <v>5565</v>
+      </c>
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
       <c r="Y19" s="5"/>
@@ -2616,7 +2706,10 @@
       <c r="M20" s="5">
         <v>112</v>
       </c>
-      <c r="N20" s="5"/>
+      <c r="N20" s="5">
+        <f>+V20-SUM(K20:M20)</f>
+        <v>115</v>
+      </c>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5">
@@ -2634,7 +2727,9 @@
       <c r="U20" s="5">
         <v>523</v>
       </c>
-      <c r="V20" s="5"/>
+      <c r="V20" s="5">
+        <v>440</v>
+      </c>
       <c r="W20" s="5"/>
       <c r="X20" s="5"/>
       <c r="Y20" s="5"/>
@@ -2714,7 +2809,10 @@
       <c r="M21" s="5">
         <v>1619</v>
       </c>
-      <c r="N21" s="5"/>
+      <c r="N21" s="5">
+        <f>+V21-SUM(K21:M21)</f>
+        <v>-1368</v>
+      </c>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5">
@@ -2732,7 +2830,10 @@
       <c r="U21" s="5">
         <v>1849</v>
       </c>
-      <c r="V21" s="5"/>
+      <c r="V21" s="13">
+        <f>743-68</f>
+        <v>675</v>
+      </c>
       <c r="W21" s="5"/>
       <c r="X21" s="5"/>
       <c r="Y21" s="5"/>
@@ -2808,7 +2909,7 @@
         <v>2769</v>
       </c>
       <c r="J22" s="5">
-        <f t="shared" ref="J22:U22" si="15">+J19-J20+J21</f>
+        <f t="shared" ref="J22:V22" si="15">+J19-J20+J21</f>
         <v>914</v>
       </c>
       <c r="K22" s="5">
@@ -2823,7 +2924,10 @@
         <f t="shared" si="15"/>
         <v>2620</v>
       </c>
-      <c r="N22" s="5"/>
+      <c r="N22" s="5">
+        <f t="shared" si="15"/>
+        <v>291</v>
+      </c>
       <c r="O22" s="5"/>
       <c r="P22" s="5">
         <f t="shared" si="15"/>
@@ -2849,7 +2953,10 @@
         <f t="shared" si="15"/>
         <v>4125</v>
       </c>
-      <c r="V22" s="5"/>
+      <c r="V22" s="5">
+        <f t="shared" si="15"/>
+        <v>5800</v>
+      </c>
       <c r="W22" s="5"/>
       <c r="X22" s="5"/>
       <c r="Y22" s="5"/>
@@ -2929,7 +3036,10 @@
       <c r="M23" s="5">
         <v>-4046</v>
       </c>
-      <c r="N23" s="5"/>
+      <c r="N23" s="5">
+        <f>+V23-SUM(K23:M23)</f>
+        <v>-40</v>
+      </c>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="5">
@@ -2947,7 +3057,9 @@
       <c r="U23" s="5">
         <v>-5758</v>
       </c>
-      <c r="V23" s="5"/>
+      <c r="V23" s="5">
+        <v>-4346</v>
+      </c>
       <c r="W23" s="5"/>
       <c r="X23" s="5"/>
       <c r="Y23" s="5"/>
@@ -3027,7 +3139,10 @@
       <c r="M24" s="5">
         <v>-14</v>
       </c>
-      <c r="N24" s="5"/>
+      <c r="N24" s="5">
+        <f>+V24-SUM(K24:M24)</f>
+        <v>-14</v>
+      </c>
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="5">
@@ -3045,7 +3160,9 @@
       <c r="U24" s="5">
         <v>-38</v>
       </c>
-      <c r="V24" s="5"/>
+      <c r="V24" s="5">
+        <v>-53</v>
+      </c>
       <c r="W24" s="5"/>
       <c r="X24" s="5"/>
       <c r="Y24" s="5"/>
@@ -3121,7 +3238,7 @@
         <v>2599</v>
       </c>
       <c r="J25" s="5">
-        <f t="shared" ref="J25:U25" si="17">+J22-J23+J24</f>
+        <f t="shared" ref="J25:V25" si="17">+J22-J23+J24</f>
         <v>6906</v>
       </c>
       <c r="K25" s="5">
@@ -3136,7 +3253,10 @@
         <f t="shared" si="17"/>
         <v>6652</v>
       </c>
-      <c r="N25" s="5"/>
+      <c r="N25" s="5">
+        <f t="shared" si="17"/>
+        <v>317</v>
+      </c>
       <c r="O25" s="5"/>
       <c r="P25" s="5">
         <f t="shared" si="17"/>
@@ -3162,7 +3282,10 @@
         <f t="shared" si="17"/>
         <v>9845</v>
       </c>
-      <c r="V25" s="5"/>
+      <c r="V25" s="5">
+        <f t="shared" si="17"/>
+        <v>10093</v>
+      </c>
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
       <c r="Y25" s="5"/>
@@ -3242,7 +3365,10 @@
       <c r="M26" s="5">
         <v>26</v>
       </c>
-      <c r="N26" s="5"/>
+      <c r="N26" s="5">
+        <f>+V26-SUM(K26:M26)</f>
+        <v>21</v>
+      </c>
       <c r="O26" s="5"/>
       <c r="P26" s="5"/>
       <c r="Q26" s="5">
@@ -3260,7 +3386,9 @@
       <c r="U26" s="5">
         <v>-11</v>
       </c>
-      <c r="V26" s="5"/>
+      <c r="V26" s="5">
+        <v>40</v>
+      </c>
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
       <c r="Y26" s="5"/>
@@ -3336,7 +3464,7 @@
         <v>2586</v>
       </c>
       <c r="J27" s="5">
-        <f t="shared" ref="J27:U27" si="19">+J25-J26</f>
+        <f t="shared" ref="J27:V27" si="19">+J25-J26</f>
         <v>6914</v>
       </c>
       <c r="K27" s="5">
@@ -3351,7 +3479,10 @@
         <f t="shared" si="19"/>
         <v>6626</v>
       </c>
-      <c r="N27" s="5"/>
+      <c r="N27" s="5">
+        <f t="shared" si="19"/>
+        <v>296</v>
+      </c>
       <c r="O27" s="5"/>
       <c r="P27" s="5">
         <f t="shared" si="19"/>
@@ -3377,7 +3508,10 @@
         <f t="shared" si="19"/>
         <v>9856</v>
       </c>
-      <c r="V27" s="5"/>
+      <c r="V27" s="5">
+        <f t="shared" si="19"/>
+        <v>10053</v>
+      </c>
       <c r="W27" s="5"/>
       <c r="X27" s="5"/>
       <c r="Y27" s="5"/>
@@ -3516,7 +3650,7 @@
         <v>1.2304559253161786</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" ref="J29:M29" si="21">+J27/J30</f>
+        <f t="shared" ref="J29:N29" si="21">+J27/J30</f>
         <v>3.3008657491972224</v>
       </c>
       <c r="K29" s="9">
@@ -3531,7 +3665,10 @@
         <f t="shared" si="21"/>
         <v>3.1791879780057388</v>
       </c>
-      <c r="N29" s="9"/>
+      <c r="N29" s="9">
+        <f t="shared" si="21"/>
+        <v>0.14194920232700778</v>
+      </c>
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="9">
@@ -3554,7 +3691,10 @@
         <f>+U27/U30</f>
         <v>4.7054285253236658</v>
       </c>
-      <c r="V29" s="5"/>
+      <c r="V29" s="9">
+        <f>+V27/V30</f>
+        <v>4.8209977398425989</v>
+      </c>
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
       <c r="Y29" s="5"/>
@@ -3636,7 +3776,9 @@
       <c r="M30" s="5">
         <v>2084.1799999999998</v>
       </c>
-      <c r="N30" s="5"/>
+      <c r="N30" s="5">
+        <v>2085.2530000000002</v>
+      </c>
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
       <c r="Q30" s="5">
@@ -3654,7 +3796,9 @@
       <c r="U30" s="5">
         <v>2094.6019999999999</v>
       </c>
-      <c r="V30" s="5"/>
+      <c r="V30" s="5">
+        <v>2085.2530000000002</v>
+      </c>
       <c r="W30" s="5"/>
       <c r="X30" s="5"/>
       <c r="Y30" s="5"/>
@@ -3769,7 +3913,7 @@
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="6">
-        <f t="shared" ref="G32:M34" si="23">+G3/C3-1</f>
+        <f t="shared" ref="G32:N34" si="23">+G3/C3-1</f>
         <v>0.14615384615384608</v>
       </c>
       <c r="H32" s="6">
@@ -3796,7 +3940,10 @@
         <f t="shared" si="23"/>
         <v>0.17391304347826098</v>
       </c>
-      <c r="N32" s="6"/>
+      <c r="N32" s="6">
+        <f t="shared" si="23"/>
+        <v>0.18128654970760238</v>
+      </c>
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
       <c r="Q32" s="6" t="e">
@@ -3819,7 +3966,10 @@
         <f>+U3/T3-1</f>
         <v>0.1399999999999999</v>
       </c>
-      <c r="V32" s="5"/>
+      <c r="V32" s="6">
+        <f>+V3/U3-1</f>
+        <v>0.18128654970760238</v>
+      </c>
       <c r="W32" s="5"/>
       <c r="X32" s="5"/>
       <c r="Y32" s="5"/>
@@ -3898,7 +4048,10 @@
         <f t="shared" si="23"/>
         <v>0.22454672245467222</v>
       </c>
-      <c r="N33" s="6"/>
+      <c r="N33" s="6">
+        <f t="shared" si="23"/>
+        <v>0.37385919165580184</v>
+      </c>
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="6" t="e">
@@ -3921,7 +4074,10 @@
         <f>+U4/T4-1</f>
         <v>0.18813237774030345</v>
       </c>
-      <c r="V33" s="5"/>
+      <c r="V33" s="6">
+        <f>+V4/U4-1</f>
+        <v>0.2034950767320145</v>
+      </c>
       <c r="W33" s="5"/>
       <c r="X33" s="5"/>
       <c r="Y33" s="5"/>
@@ -4000,7 +4156,10 @@
         <f t="shared" si="23"/>
         <v>0.2139701754814145</v>
       </c>
-      <c r="N34" s="6"/>
+      <c r="N34" s="6">
+        <f t="shared" si="23"/>
+        <v>0.34187840803674452</v>
+      </c>
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="6" t="e">
@@ -4023,7 +4182,10 @@
         <f>+U5/T5-1</f>
         <v>0.18066949552098066</v>
       </c>
-      <c r="V34" s="5"/>
+      <c r="V34" s="6">
+        <f>+V5/U5-1</f>
+        <v>0.18848949150043315</v>
+      </c>
       <c r="W34" s="5"/>
       <c r="X34" s="5"/>
       <c r="Y34" s="5"/>
@@ -4083,7 +4245,7 @@
         <v>0.25337147527584802</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" ref="I35:M38" si="28">I8/E8-1</f>
+        <f t="shared" ref="I35:N38" si="28">I8/E8-1</f>
         <v>0.26385328337605984</v>
       </c>
       <c r="J35" s="6">
@@ -4102,7 +4264,10 @@
         <f t="shared" si="28"/>
         <v>0.19862693087845207</v>
       </c>
-      <c r="N35" s="6"/>
+      <c r="N35" s="6">
+        <f t="shared" si="28"/>
+        <v>0.18709304008103023</v>
+      </c>
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
       <c r="Q35" s="6" t="e">
@@ -4125,7 +4290,10 @@
         <f>+U8/T8-1</f>
         <v>0.2649757966922146</v>
       </c>
-      <c r="V35" s="5"/>
+      <c r="V35" s="6">
+        <f>+V8/U8-1</f>
+        <v>0.18268425877944749</v>
+      </c>
       <c r="W35" s="5"/>
       <c r="X35" s="5"/>
       <c r="Y35" s="5"/>
@@ -4204,7 +4372,10 @@
         <f t="shared" si="28"/>
         <v>0.29020172910662834</v>
       </c>
-      <c r="N36" s="6"/>
+      <c r="N36" s="6">
+        <f t="shared" si="28"/>
+        <v>0.29658097005035788</v>
+      </c>
       <c r="O36" s="5"/>
       <c r="P36" s="6"/>
       <c r="Q36" s="6" t="e">
@@ -4227,7 +4398,10 @@
         <f>+U9/T9-1</f>
         <v>0.12667977712225498</v>
       </c>
-      <c r="V36" s="5"/>
+      <c r="V36" s="6">
+        <f>+V9/U9-1</f>
+        <v>0.25439999999999996</v>
+      </c>
       <c r="W36" s="5"/>
       <c r="X36" s="5"/>
       <c r="Y36" s="5"/>
@@ -4306,7 +4480,10 @@
         <f t="shared" si="28"/>
         <v>-7.6394194041251584E-4</v>
       </c>
-      <c r="N37" s="6"/>
+      <c r="N37" s="6">
+        <f t="shared" si="28"/>
+        <v>-3.9215686274509665E-3</v>
+      </c>
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
       <c r="Q37" s="6" t="e">
@@ -4329,7 +4506,10 @@
         <f>+U10/T10-1</f>
         <v>-1.9828408007626308E-2</v>
       </c>
-      <c r="V37" s="5"/>
+      <c r="V37" s="6">
+        <f>+V10/U10-1</f>
+        <v>-8.169616806068869E-3</v>
+      </c>
       <c r="W37" s="5"/>
       <c r="X37" s="5"/>
       <c r="Y37" s="5"/>
@@ -4408,7 +4588,10 @@
         <f t="shared" si="28"/>
         <v>0.20370039327851264</v>
       </c>
-      <c r="N38" s="10"/>
+      <c r="N38" s="10">
+        <f t="shared" si="28"/>
+        <v>0.20127100928171249</v>
+      </c>
       <c r="O38" s="5"/>
       <c r="P38" s="5"/>
       <c r="Q38" s="5"/>
@@ -4428,7 +4611,10 @@
         <f>+U11/T11-1</f>
         <v>0.17963573938467325</v>
       </c>
-      <c r="V38" s="5"/>
+      <c r="V38" s="10">
+        <f>+V11/U11-1</f>
+        <v>0.18279594342625849</v>
+      </c>
       <c r="W38" s="5"/>
       <c r="X38" s="5"/>
       <c r="Y38" s="5"/>
@@ -4516,10 +4702,13 @@
         <v>0.3983874792506521</v>
       </c>
       <c r="M39" s="6">
-        <f t="shared" ref="M39" si="39">+M13/M11</f>
+        <f t="shared" ref="M39:N39" si="39">+M13/M11</f>
         <v>0.39786143907329025</v>
       </c>
-      <c r="N39" s="6"/>
+      <c r="N39" s="6">
+        <f t="shared" si="39"/>
+        <v>0.39572601976889876</v>
+      </c>
       <c r="O39" s="5"/>
       <c r="P39" s="6" t="e">
         <f t="shared" ref="P39:U39" si="40">+P13/P11</f>
@@ -4545,7 +4734,10 @@
         <f t="shared" si="40"/>
         <v>0.39399245077083994</v>
       </c>
-      <c r="V39" s="5"/>
+      <c r="V39" s="6">
+        <f t="shared" ref="V39" si="41">+V13/V11</f>
+        <v>0.39754311090604993</v>
+      </c>
       <c r="W39" s="5"/>
       <c r="X39" s="5"/>
       <c r="Y39" s="5"/>
@@ -4593,23 +4785,23 @@
         <v>45</v>
       </c>
       <c r="C40" s="6">
-        <f t="shared" ref="C40:G40" si="41">+C19/C11</f>
+        <f t="shared" ref="C40:G40" si="42">+C19/C11</f>
         <v>-2.9695115040235746E-2</v>
       </c>
       <c r="D40" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>3.5319609967497292E-2</v>
       </c>
       <c r="E40" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>4.240206629358588E-2</v>
       </c>
       <c r="F40" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.5619967793880837E-2</v>
       </c>
       <c r="G40" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1.6977593524824794E-2</v>
       </c>
       <c r="H40" s="6">
@@ -4617,52 +4809,58 @@
         <v>7.3925233644859811E-2</v>
       </c>
       <c r="I40" s="6">
-        <f t="shared" ref="I40:J40" si="42">+I19/I11</f>
+        <f t="shared" ref="I40:J40" si="43">+I19/I11</f>
         <v>9.4833750446907394E-2</v>
       </c>
       <c r="J40" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>6.4804749561000088E-2</v>
       </c>
       <c r="K40" s="6">
-        <f t="shared" ref="K40:L40" si="43">+K19/K11</f>
+        <f t="shared" ref="K40:L40" si="44">+K19/K11</f>
         <v>0.10647706581115061</v>
       </c>
       <c r="L40" s="6">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.11461544541933444</v>
       </c>
       <c r="M40" s="6">
-        <f t="shared" ref="M40" si="44">+M19/M11</f>
+        <f t="shared" ref="M40:N40" si="45">+M19/M11</f>
         <v>8.2646469146803292E-2</v>
       </c>
-      <c r="N40" s="6"/>
+      <c r="N40" s="6">
+        <f t="shared" si="45"/>
+        <v>0.12348600863149102</v>
+      </c>
       <c r="O40" s="5"/>
       <c r="P40" s="6" t="e">
-        <f t="shared" ref="P40:U40" si="45">+P19/P11</f>
+        <f t="shared" ref="P40:U40" si="46">+P19/P11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q40" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-0.43657419876110959</v>
       </c>
       <c r="R40" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-0.2196505299341163</v>
       </c>
       <c r="S40" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-5.7470903786429085E-2</v>
       </c>
       <c r="T40" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2.9773879456023174E-2</v>
       </c>
       <c r="U40" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>6.3645459093182949E-2</v>
       </c>
-      <c r="V40" s="5"/>
+      <c r="V40" s="6">
+        <f t="shared" ref="V40" si="47">+V19/V11</f>
+        <v>0.10698425514735567</v>
+      </c>
       <c r="W40" s="5"/>
       <c r="X40" s="5"/>
       <c r="Y40" s="5"/>
@@ -4710,23 +4908,23 @@
         <v>46</v>
       </c>
       <c r="C41" s="6">
-        <f t="shared" ref="C41:G41" si="46">+C23/C22</f>
+        <f t="shared" ref="C41:G41" si="48">+C23/C22</f>
         <v>0</v>
       </c>
       <c r="D41" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="E41" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-0.22727272727272727</v>
       </c>
       <c r="F41" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>9.6311475409836061E-2</v>
       </c>
       <c r="G41" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-4.6031746031746035E-2</v>
       </c>
       <c r="H41" s="6">
@@ -4734,52 +4932,58 @@
         <v>5.3171641791044777E-2</v>
       </c>
       <c r="I41" s="6">
-        <f t="shared" ref="I41:J41" si="47">+I23/I22</f>
+        <f t="shared" ref="I41:J41" si="49">+I23/I22</f>
         <v>5.7060310581437339E-2</v>
       </c>
       <c r="J41" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-6.566739606126915</v>
       </c>
       <c r="K41" s="6">
-        <f t="shared" ref="K41:L41" si="48">+K23/K22</f>
+        <f t="shared" ref="K41:L41" si="50">+K23/K22</f>
         <v>-0.29025270758122745</v>
       </c>
       <c r="L41" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>9.4414893617021281E-2</v>
       </c>
       <c r="M41" s="6">
-        <f t="shared" ref="M41" si="49">+M23/M22</f>
+        <f t="shared" ref="M41:N41" si="51">+M23/M22</f>
         <v>-1.5442748091603054</v>
       </c>
-      <c r="N41" s="6"/>
+      <c r="N41" s="6">
+        <f t="shared" si="51"/>
+        <v>-0.13745704467353953</v>
+      </c>
       <c r="O41" s="5"/>
       <c r="P41" s="6" t="e">
-        <f t="shared" ref="P41:U41" si="50">+P23/P22</f>
+        <f t="shared" ref="P41:U41" si="52">+P23/P22</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q41" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>2.7641808234955371E-2</v>
       </c>
       <c r="R41" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.48</v>
       </c>
       <c r="S41" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>1.9202206662423085E-2</v>
       </c>
       <c r="T41" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>9.1770788453252913E-2</v>
       </c>
       <c r="U41" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>-1.3958787878787879</v>
       </c>
-      <c r="V41" s="5"/>
+      <c r="V41" s="6">
+        <f t="shared" ref="V41" si="53">+V23/V22</f>
+        <v>-0.74931034482758618</v>
+      </c>
       <c r="W41" s="5"/>
       <c r="X41" s="5"/>
       <c r="Y41" s="5"/>
